--- a/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0016.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0016.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Sawring - Stage 1 DMG Blitz</t>
+          <t>Sawring - Sát Thương Giai Đoạn 1 Blitz</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Lưỡi Cưa Xoay - Stage 2 Blitz: Sát Thương</t>
+          <t>Lưỡi Cưa Xoay - Giai Đoạn 2 Blitz: Sát Thương</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Lưỡi Cưa Xoay - Stage 3 Blitz: Sát Thương</t>
+          <t>Lưỡi Cưa Xoay - Giai Đoạn 3 Blitz: Sát Thương</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>DMG của Sawring - Eradication</t>
+          <t>Bản Giao Hưởng Diệt Trừ: Sát Thương</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Hệ Số Sát Thương Bonus Mỗi Vòng Chainsaw</t>
+          <t>Hệ Số Sát Thương Phần Thưởng Mỗi Vòng Cưa Xích</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>{0} Tấn Công</t>
+          <t>{0} ATK</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Bản Giao Hưởng Diệt Trừ - Shield</t>
+          <t>Bản Giao Hưởng Diệt Trừ - Khiên</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>{0} Tấn Công</t>
+          <t>{0} ATK</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Concerto Regen của Sawring - Eradication</t>
+          <t>Bản Giao Hưởng Diệt Trừ - Hồi Phục</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Bản Giao Hưởng Diệt Trừ - Energy Regen Resonance</t>
+          <t>Bản Giao Hưởng Diệt Trừ - Hồi Resonance Energy</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Lưỡi Cưa Xoay - Stage 2 Blitz (Giữ): Sát Thương</t>
+          <t>Lưỡi Cưa Xoay - Giai Đoạn 2 Blitz (Giữ): Sát Thương</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Lưỡi Cưa Xoay - Stage 3 Blitz (Giữ): Sát Thương</t>
+          <t>Lưỡi Cưa Xoay - Giai Đoạn 3 Blitz (Giữ): Sát Thương</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Lưỡi Cưa Xoay - Stage 2 Blitz: Sát Thương Tacet Discord</t>
+          <t>Lưỡi Cưa Xoay - Giai Đoạn 2 Blitz: Discordance DMG</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Lưỡi Cưa Xoay - Stage 3 Blitz: Sát Thương Falltone</t>
+          <t>Lưỡi Cưa Xoay - Giai Đoạn 3 Blitz: Falltone DMG</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Chế Độ Chainsaw - Sát Thương Dodge Đòn Phản Công</t>
+          <t>Chế Độ Cưa Xích - Sát Thương Né Đòn Phản Công</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Chế Độ Chainsaw - Sát Thương Giữ Dodge Đòn Phản Công</t>
+          <t>Chế Độ Cưa Xích - Sát Thương Giữ Né Đòn Phản Công</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Sát thương Giai đoạn 1 Basic Attack</t>
+          <t>DMG Giai đoạn 1 Basic Attack</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Sát thương Giai đoạn 2 Basic Attack</t>
+          <t>DMG Giai đoạn 2 Basic Attack</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Sát thương Giai đoạn 3 Basic Attack</t>
+          <t>DMG Giai đoạn 3 Basic Attack</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>DMG của Lynae-Style Palettes</t>
+          <t>Sát Thương Bộ Bảng Màu Lynae</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>DMG của Additive Color</t>
+          <t>Sát Thương Cộng Hưởng Màu</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Sát Thương Prismatic Overblast</t>
+          <t>Sát Thương Vụ Nổ Sắc Cầu</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Kaleidoscopic Parade - Basic Attack Stage 1 Sát Thương</t>
+          <t>Diễu Hành Đa Sắc - Basic Attack Giai Đoạn 1 Sát Thương</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Diễu Hành Sắc Màu - Sát thương Basic Attack Giai đoạn 2</t>
+          <t>Diễu Hành Sắc Màu - DMG Basic Attack Giai đoạn 2</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Diễu Hành Sắc Màu - Sát thương Basic Attack Giai đoạn 3</t>
+          <t>Diễu Hành Sắc Màu - DMG Basic Attack Giai đoạn 3</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Diễu Hành Sắc Màu - Sát thương Basic Attack Giai đoạn 4</t>
+          <t>Diễu Hành Sắc Màu - DMG Basic Attack Giai đoạn 4</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Diễu Hành Sắc Màu - Sát thương Basic Attack Giai đoạn 5</t>
+          <t>Diễu Hành Sắc Màu - DMG Basic Attack Giai đoạn 5</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Dodge Counter của Kaleidoscopic Parade</t>
+          <t>Diễu Hành Sắc Màu - Dodge Counter Tránh</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Diễu Hành Sắc Màu - Sát thương Heavy Attack Đất</t>
+          <t>Diễu Hành Sắc Màu - DMG Heavy Attack Đất</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Diễu Hành Sắc Màu - Sát thương Bùng Nổ Graffiti</t>
+          <t>Diễu Hành Sắc Màu - DMG Bùng Nổ Graffiti</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Diễu Hành Sắc Màu - Sát thương Mid-air Attack</t>
+          <t>Diễu Hành Sắc Màu - DMG Tấn Công Giữa Không</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Phân tích Phổ - Sát thương Giai điệu Tacet Discord</t>
+          <t>Phân tích Phổ - DMG Giai điệu Tacet Discord</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Diễu Hành Sắc Màu - Sát thương Heavy Attack Giữa Không</t>
+          <t>Diễu Hành Sắc Màu - DMG Heavy Attack Giữa Không</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Time to Show Some Colors! Sát Thương</t>
+          <t>Đến lúc thể hiện bản lĩnh rồi! Sát Thương</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Khúc Giao Hưởng Hồi Phục Prismatic Overblast</t>
+          <t>Khúc Giao Hưởng Hồi Phục Vụ Nổ Sắc Cầu</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Tune Rupture Response - Sát thương Spectral Analysis</t>
+          <t>Phản ứng Tune Rupture - DMG Spectral Analysis</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>{0} Tune AMP</t>
+          <t>{0} Điều chỉnh AMP</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Basic Attack - Thời Gian Cooldown Tác Động Hình Ảnh</t>
+          <t>Basic Attack - Thời gian hồi Chiêu Tác Động Hình Ảnh</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Diễu Hành Sắc Màu - Chi phí Thể Lực cho mỗi đòn Heavy Attack Đất</t>
+          <t>Diễu Hành Sắc Màu - Chi phí STA cho mỗi đòn Heavy Attack Đất</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Lễ Hội Sắc Màu - Tiêu Hao STA Heavy Attack Giữa Không</t>
+          <t>Lễ Hội Sắc Màu - Tiêu Hao STA Đòn Heavy Attack Giữa Không</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Diễu Hành Sắc Màu - Chi phí Thể Lực cho Mid-air Attack</t>
+          <t>Diễu Hành Sắc Màu - Chi phí STA cho Tấn Công Giữa Không</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Thời Gian Cooldown Lynae-Style Palettes</t>
+          <t>Thời gian hồi Chiêu Bảng Màu Kiểu Lynae</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Cooldown của Additive Color</t>
+          <t>Thời gian hồi Phục Màu Cộng</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Tiêu hao Resonance Energy</t>
+          <t>Chi Phí Resonance Energy</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Stage 1 DMG</t>
+          <t>Sát Thương Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Stage 2 DMG</t>
+          <t>Sát Thương Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Stage 3 DMG</t>
+          <t>Sát Thương Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Stage 4 DMG</t>
+          <t>Sát Thương Giai Đoạn 4</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>DMG Giai đoạn 5</t>
+          <t>Sát Thương Giai Đoạn 5</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack</t>
+          <t>Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Chi phí Thể lực cho Heavy Attack</t>
+          <t>Chi phí STA cho Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Resonance Cost</t>
+          <t>Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>DMG của Devastation</t>
+          <t>Sát thương Tàn phá</t>
         </is>
       </c>
     </row>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Umbra: Sát Thương Basic Attack Stage 1</t>
+          <t>Umbra: Sát Thương Basic Attack Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Umbra: Sát Thương Basic Attack Stage 2</t>
+          <t>Umbra: Sát Thương Basic Attack Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Stage 1 DMG</t>
+          <t>Sát Thương Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Stage 2 DMG</t>
+          <t>Sát Thương Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Stage 3 DMG</t>
+          <t>Sát Thương Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Stage 4 DMG</t>
+          <t>Sát Thương Giai Đoạn 4</t>
         </is>
       </c>
     </row>
@@ -6229,7 +6229,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack</t>
+          <t>Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6359,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Chi phí Thể lực cho Heavy Attack</t>
+          <t>Chi phí STA cho Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -7009,7 +7009,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Resonance Cost</t>
+          <t>Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Stage 1 DMG</t>
+          <t>Sát Thương Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Stage 2 DMG</t>
+          <t>Sát Thương Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Stage 3 DMG</t>
+          <t>Sát Thương Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Concerto Regen Giai đoạn 1</t>
+          <t>Hồi Phục Giao Hưởng Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Concerto Regen Giai đoạn 2</t>
+          <t>Hồi Phục Giao Hưởng Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Concerto Regen Giai đoạn 3</t>
+          <t>Hồi Phục Giao Hưởng Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Stage 1 DMG</t>
+          <t>Sát Thương Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Stage 2 DMG</t>
+          <t>Sát Thương Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Stage 3 DMG</t>
+          <t>Sát Thương Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack</t>
+          <t>Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>DMG của Delusive Dive</t>
+          <t>Sát Thương Delusive Dive</t>
         </is>
       </c>
     </row>
@@ -8114,7 +8114,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Chi phí Thể lực cho Heavy Attack</t>
+          <t>Chi phí STA cho Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>STA Cost của Delusive Dive</t>
+          <t>Chi Phí STA Delusive Dive</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>DMG của Graceful Step</t>
+          <t>Sát Thương Bước Nhẹ</t>
         </is>
       </c>
     </row>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>DMG của Flickering Reverie</t>
+          <t>Sát Thương Bản Giao Hưởng Ảo Ảnh</t>
         </is>
       </c>
     </row>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>DMG của Jolt</t>
+          <t>DMG Jolt</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Thời Gian Cooldown Bước Nhẹ</t>
+          <t>Thời gian hồi Chiêu Bước Nhẹ</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Thời Gian Cooldown Bản Giao Hưởng Ảo Ảnh</t>
+          <t>Thời gian hồi Chiêu Bản Giao Hưởng Ảo Ảnh</t>
         </is>
       </c>
     </row>
@@ -8829,7 +8829,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Concerto Regen của Graceful Step</t>
+          <t>Hồi Phục Bản Giao Hưởng Bước Nhẹ</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Concerto Regen của Flickering Reverie</t>
+          <t>Hồi Phục Bản Giao Hưởng Ảo Ảnh</t>
         </is>
       </c>
     </row>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>DMG Giai đoạn 1 của Phantom Sting</t>
+          <t>Sát Thương Giai Đoạn 1 - Đốt Cháy Ảo Giác</t>
         </is>
       </c>
     </row>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>DMG Giai đoạn 2 của Phantom Sting</t>
+          <t>Sát Thương Giai Đoạn 2 - Đốt Cháy Ảo Giác</t>
         </is>
       </c>
     </row>
@@ -9219,7 +9219,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>DMG Giai đoạn 3 của Phantom Sting</t>
+          <t>Sát Thương Giai Đoạn 3 - Đốt Cháy Ảo Giác</t>
         </is>
       </c>
     </row>
@@ -9284,7 +9284,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>DMG của Abysmal Vortex</t>
+          <t>DMG Xoáy Vực Sâu</t>
         </is>
       </c>
     </row>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>DMG của Perception Drain</t>
+          <t>Sát Thương Thấm Hụt Nhận Thức</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>DMG của Shadowy Sweep</t>
+          <t>Sát Thương Quét Bóng Tối</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Hồi máu khi tiêu hao Trance</t>
+          <t>Hồi phục bằng Trance Tiêu Hao</t>
         </is>
       </c>
     </row>
@@ -9544,7 +9544,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>{0} Tấn Công</t>
+          <t>{0} ATK</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Healing Thấm Hụt Nhận Thức</t>
+          <t>Hồi Phục Thấm Hụt Nhận Thức</t>
         </is>
       </c>
     </row>
@@ -9739,7 +9739,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>STA Cost của Abysmal Vortex</t>
+          <t>Chi phí STA Xoáy Vực Sâu</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Thời Gian Tồn Tại Mirage</t>
+          <t>Thời Gian Tồn Tại Ảo Ảnh</t>
         </is>
       </c>
     </row>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Thời Gian Cooldown Thấm Hụt Nhận Thức</t>
+          <t>Thời gian hồi Chiêu Thấm Hụt Nhận Thức</t>
         </is>
       </c>
     </row>
@@ -9999,7 +9999,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Concerto Regen của Perception Drain</t>
+          <t>Hồi Phục Bản Giao Hưởng Thấm Hụt Nhận Thức</t>
         </is>
       </c>
     </row>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>DMG của Flowing Suffocation</t>
+          <t>Sát Thương Ngạt Thở</t>
         </is>
       </c>
     </row>
@@ -10194,7 +10194,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>DMG của Diffusion</t>
+          <t>Sát Thương Khuếch Tán</t>
         </is>
       </c>
     </row>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Thời Gian Cooldown Ngạt Thở</t>
+          <t>Thời gian hồi Chiêu Ngạt Thở</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Resonance Cost</t>
+          <t>Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Concerto Regen của Flowing Suffocation</t>
+          <t>Khúc Giao Hưởng Ngạt Thở Tái Sinh</t>
         </is>
       </c>
     </row>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>DMG của Ripple</t>
+          <t>Sát Thương Sóng</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>DMG của Tidal Surge</t>
+          <t>Sát Thương Sóng Thủy Triều</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Concerto Regen của Ripple</t>
+          <t>Hồi Phục Giao Hưởng Sóng</t>
         </is>
       </c>
     </row>
@@ -10649,7 +10649,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Concerto Regen của Tidal Surge</t>
+          <t>Hồi phục Bản hòa tấu Sóng Thủy Triều</t>
         </is>
       </c>
     </row>
@@ -10714,7 +10714,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>STA Cost của Phantom Sting giữa không trung</t>
+          <t>Chi phí STA cho Kỹ Năng Phantom Sting trên không</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Stage 1 DMG</t>
+          <t>Sát Thương Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Stage 2 DMG</t>
+          <t>Sát Thương Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -10909,7 +10909,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Stage 3 DMG</t>
+          <t>Sát Thương Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack</t>
+          <t>Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -11039,7 +11039,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>DMG của Scarlet Coda</t>
+          <t>Sát Thương Khúc Kết Đỏ Thẫm</t>
         </is>
       </c>
     </row>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Increase Hệ Số Sát Thương sau Mỗi Âm Vang</t>
+          <t>Tăng Hệ Số Sát Thương sau Mỗi Âm Vang</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -11299,7 +11299,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Concerto Regen của Scarlet Coda</t>
+          <t>Hồi Phục Khúc Kết Đỏ Thẫm</t>
         </is>
       </c>
     </row>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Chi phí Thể lực cho Heavy Attack</t>
+          <t>Chi phí STA cho Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>STA Cost của Scarlet Coda</t>
+          <t>Chi Phí Tần Số Scarlet Coda</t>
         </is>
       </c>
     </row>
@@ -11559,7 +11559,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -11689,7 +11689,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -11819,7 +11819,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Basic Attack - Hecate Stage 1 Sát Thương</t>
+          <t>Basic Attack - Hecate Giai Đoạn 1 Sát Thương</t>
         </is>
       </c>
     </row>
@@ -11884,7 +11884,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Basic Attack - Hecate Stage 2 Sát Thương</t>
+          <t>Basic Attack - Hecate Giai Đoạn 2 Sát Thương</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Basic Attack - Stage 3 DMG Hecate</t>
+          <t>Basic Attack - Sát Thương Giai Đoạn 3 Hecate</t>
         </is>
       </c>
     </row>
@@ -12014,7 +12014,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Attack Nâng Cao - Hecate: Sát Thương Strings</t>
+          <t>Tấn Công Nâng Cao - Hecate: Strings DMG</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Attack Nâng Cao - Hecate: Sát Thương Winds</t>
+          <t>Tấn Công Nâng Cao - Hecate: Winds DMG</t>
         </is>
       </c>
     </row>
@@ -12144,7 +12144,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Attack Nâng Cao - Hecate: Sát Thương Cadenza</t>
+          <t>Tấn Công Nâng Cao - Hecate: Cadenza DMG</t>
         </is>
       </c>
     </row>
@@ -12209,7 +12209,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Sát thương Curtain Call</t>
+          <t>DMG Điểm cuối màn diễn</t>
         </is>
       </c>
     </row>
@@ -12274,7 +12274,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Hồi Phục Bản Giao Hưởng Waltz of Forsaken Depths</t>
+          <t>Hồi Phục Bản Giao Hưởng Điệu Van-xơ Vực Thẳm Bị Lãng Quên</t>
         </is>
       </c>
     </row>
@@ -12339,7 +12339,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Thời gian của Waltz of Forsaken Depths</t>
+          <t>Thời Gian Vũ Điệu Vực Thẳm Bị Lãng Quên</t>
         </is>
       </c>
     </row>
@@ -12469,7 +12469,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>DMG của Suite of Quietus</t>
+          <t>Sát Thương Bộ Tịch Tĩnh</t>
         </is>
       </c>
     </row>
@@ -12534,7 +12534,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>DMG của Suite of Immortality</t>
+          <t>Sát Thương Bộ Vô Tận</t>
         </is>
       </c>
     </row>
@@ -12599,7 +12599,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Hồi Concerto Energy Bộ Suite of Quietus</t>
+          <t>Hồi Phục Bản Giao Hưởng Bộ Tịch Tĩnh</t>
         </is>
       </c>
     </row>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Hồi Concerto Energy Bộ Suite of Immortality</t>
+          <t>Bản Concerto Trường Sinh Hồi Phục</t>
         </is>
       </c>
     </row>
@@ -12729,7 +12729,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Sát Thương Fate Cuối Cùng</t>
+          <t>Sát Thương Định Mệnh Cuối Cùng</t>
         </is>
       </c>
     </row>
@@ -12794,7 +12794,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Sát thương Giấc Mơ Ma Quái Thì Thầm</t>
+          <t>DMG Giấc Mơ Ma Quái Thì Thầm</t>
         </is>
       </c>
     </row>
@@ -12859,7 +12859,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Thời Gian Cooldown Khúc Kết Đỏ Thẫm</t>
+          <t>Thời gian hồi Chiêu Khúc Kết Đỏ Thẫm</t>
         </is>
       </c>
     </row>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Stage 1 DMG</t>
+          <t>Sát Thương Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Stage 2 DMG</t>
+          <t>Sát Thương Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -13119,7 +13119,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Stage 3 DMG</t>
+          <t>Sát Thương Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Stage 4 DMG</t>
+          <t>Sát Thương Giai Đoạn 4</t>
         </is>
       </c>
     </row>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>DMG Giai đoạn 5</t>
+          <t>Sát Thương Giai Đoạn 5</t>
         </is>
       </c>
     </row>
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack</t>
+          <t>Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -13379,7 +13379,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Chi phí Thể lực cho Heavy Attack</t>
+          <t>Chi phí STA cho Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -13444,7 +13444,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Stage 1 DMG Mid-air Attack</t>
+          <t>Sát Thương Giai Đoạn 1 Mid-air Attack</t>
         </is>
       </c>
     </row>
@@ -13509,7 +13509,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Stage 2 DMG Mid-air Attack</t>
+          <t>Sát Thương Giai Đoạn 2 Mid-air Attack</t>
         </is>
       </c>
     </row>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Stage 3 Đòn Mid-air Attack: Sát Thương</t>
+          <t>Giai Đoạn 3 Đòn Mid-air Attack: Sát Thương</t>
         </is>
       </c>
     </row>
@@ -13704,7 +13704,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack Trên Không</t>
+          <t>Sát Thương Đòn Tấn Công Mạnh Trên Không</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Tiêu Hao STA Heavy Attack Trên Không</t>
+          <t>Tiêu Hao STA Đòn Tấn Công Mạnh Trên Không</t>
         </is>
       </c>
     </row>
@@ -13834,7 +13834,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -13899,7 +13899,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -13964,7 +13964,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -14159,7 +14159,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Healing Thịnh Vượng Của Cây</t>
+          <t>Hồi Phục Thịnh Vượng Của Cây</t>
         </is>
       </c>
     </row>
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>{0} Tấn Công</t>
+          <t>{0} ATK</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Sát Thương Attack Phối Hợp</t>
+          <t>Sát Thương Tấn Công Phối Hợp</t>
         </is>
       </c>
     </row>
@@ -14354,7 +14354,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Hồi máu khi Tấn công Phối hợp</t>
+          <t>Hồi phục tấn công phối hợp</t>
         </is>
       </c>
     </row>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>{0} Tấn Công</t>
+          <t>{0} ATK</t>
         </is>
       </c>
     </row>
@@ -14484,7 +14484,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Thời gian duy trì Dấu Hiệu Quang Hợp</t>
+          <t>Thời Gian Dấu Hiệu Quang Hợp</t>
         </is>
       </c>
     </row>
@@ -14614,7 +14614,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -14744,7 +14744,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Resonance Cost</t>
+          <t>Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Heavy Attack: Sát Thương Starflower Nở</t>
+          <t>Đòn Heavy Attack: Sát Thương Hoa Sao Nở</t>
         </is>
       </c>
     </row>
@@ -14939,7 +14939,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Healing Starflower Nở Rộ</t>
+          <t>Hồi Phục Hoa Sao Nở Rộ</t>
         </is>
       </c>
     </row>
@@ -15004,7 +15004,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>{0} Tấn Công</t>
+          <t>{0} ATK</t>
         </is>
       </c>
     </row>
@@ -15069,7 +15069,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Stage 1 DMG</t>
+          <t>Sát Thương Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Stage 2 DMG</t>
+          <t>Sát Thương Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -15199,7 +15199,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Stage 3 DMG</t>
+          <t>Sát Thương Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -15264,7 +15264,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Stage 4 DMG</t>
+          <t>Sát Thương Giai Đoạn 4</t>
         </is>
       </c>
     </row>
@@ -15459,7 +15459,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack</t>
+          <t>Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -15524,7 +15524,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Chi phí Thể lực cho Heavy Attack (mỗi giây)</t>
+          <t>Chi phí STA cho Heavy Attack (mỗi giây)</t>
         </is>
       </c>
     </row>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Healing</t>
+          <t>Hồi Phục</t>
         </is>
       </c>
     </row>
@@ -15784,7 +15784,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -15914,7 +15914,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Healing Kết Hợp Nhất Thời</t>
+          <t>Hồi Phục Kết Hợp Nhất Thời</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>DMG gây lên Thực Thể Tàn Dư</t>
+          <t>Sát Thương Thực Thể Dư</t>
         </is>
       </c>
     </row>
@@ -16174,7 +16174,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Healing Thực Thể Dư</t>
+          <t>Hồi Phục Thực Thể Dư</t>
         </is>
       </c>
     </row>
@@ -16304,7 +16304,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Resonance Cost</t>
+          <t>Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -16499,7 +16499,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -16564,7 +16564,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Healing Concentration</t>
+          <t>Hồi Phục Tập Trung</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Healing Sương Giá Tràn Đầy</t>
+          <t>Hồi Phục Sương Giá Tràn Đầy</t>
         </is>
       </c>
     </row>
@@ -16759,7 +16759,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -16824,7 +16824,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Stage 1 DMG</t>
+          <t>Sát Thương Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -16889,7 +16889,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Stage 2 DMG</t>
+          <t>Sát Thương Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Stage 3 DMG</t>
+          <t>Sát Thương Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -17019,7 +17019,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Stage 4 DMG</t>
+          <t>Sát Thương Giai Đoạn 4</t>
         </is>
       </c>
     </row>
@@ -17084,7 +17084,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>DMG Giai đoạn 5</t>
+          <t>Sát Thương Giai Đoạn 5</t>
         </is>
       </c>
     </row>
@@ -17149,7 +17149,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack</t>
+          <t>Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -17279,7 +17279,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Chi phí Thể lực cho Heavy Attack</t>
+          <t>Chi phí STA cho Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -17474,7 +17474,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -17669,7 +17669,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -17734,7 +17734,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -17799,7 +17799,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Resonance Cost</t>
+          <t>Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -17994,7 +17994,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Detonate Sát thương</t>
+          <t>Kích nổ Sát thương</t>
         </is>
       </c>
     </row>
@@ -18059,7 +18059,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Sát Thương Khúc Nổ Glacier</t>
+          <t>Sát Thương Khúc Nổ Băng Hà</t>
         </is>
       </c>
     </row>
@@ -18124,7 +18124,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Sát Thương Nổ Ice Prism</t>
+          <t>Sát Thương Nổ Lăng Kính Băng</t>
         </is>
       </c>
     </row>
@@ -18189,7 +18189,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Sát Thương Nổ Ice Thorn</t>
+          <t>Sát Thương Nổ Gai Băng</t>
         </is>
       </c>
     </row>
@@ -18254,7 +18254,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Thời gian duy trì Clarity</t>
+          <t>Thời gian sáng suốt</t>
         </is>
       </c>
     </row>
@@ -18319,7 +18319,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Kích nổ Concerto Energy</t>
+          <t>Kích nổ Năng lượng Concerto</t>
         </is>
       </c>
     </row>
@@ -18449,7 +18449,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Hồi Phục Khúc Nổ Glacier</t>
+          <t>Hồi Phục Khúc Nổ Băng Hà</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Hồi Phục Liên Khúc Nổ Ice Prism</t>
+          <t>Hồi Phục Liên Khúc Nổ Lăng Kính Băng</t>
         </is>
       </c>
     </row>
@@ -18579,7 +18579,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Stage 1 DMG</t>
+          <t>Sát Thương Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Stage 2 DMG</t>
+          <t>Sát Thương Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -18839,7 +18839,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Stage 3 DMG</t>
+          <t>Sát Thương Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -18904,7 +18904,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Stage 4 DMG</t>
+          <t>Sát Thương Giai Đoạn 4</t>
         </is>
       </c>
     </row>
@@ -18969,7 +18969,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack</t>
+          <t>Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -19034,7 +19034,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Heavy Attack - Resonance Sát Thương</t>
+          <t>Heavy Attack - Cộng Hưởng Sát Thương</t>
         </is>
       </c>
     </row>
@@ -19099,7 +19099,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Heavy Attack - Aftertune Sát Thương</t>
+          <t>Đòn Tấn Công Mạnh - Aftertune Sát Thương</t>
         </is>
       </c>
     </row>
@@ -19229,7 +19229,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Chi phí Thể lực cho Heavy Attack</t>
+          <t>Chi phí STA cho Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -19359,7 +19359,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -19424,7 +19424,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -19619,7 +19619,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>DMG vụ nổ</t>
+          <t>Sát thương nổ</t>
         </is>
       </c>
     </row>
@@ -19749,7 +19749,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -19879,7 +19879,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Resonance Cost</t>
+          <t>Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -19944,7 +19944,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Hồi Concerto</t>
+          <t>Hồi Phục Giao Hưởng</t>
         </is>
       </c>
     </row>
@@ -20009,7 +20009,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Stage 1 DMG</t>
+          <t>Sát Thương Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Stage 2 DMG</t>
+          <t>Sát Thương Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -20269,7 +20269,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Stage 3 DMG</t>
+          <t>Sát Thương Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack</t>
+          <t>Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -20464,7 +20464,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Chi phí Thể lực cho Heavy Attack</t>
+          <t>Chi phí STA cho Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>DMG Carmine Gleam</t>
+          <t>Sát Thương Lấp Lánh Carmine</t>
         </is>
       </c>
     </row>
@@ -20659,7 +20659,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Giai Đoạn Erosion Đỏ Thẫm 1 - Sát Thương</t>
+          <t>Giai Đoạn Xói Mòn Đỏ Thẫm 1 - Sát Thương</t>
         </is>
       </c>
     </row>
@@ -20724,7 +20724,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Giai Đoạn Erosion Đỏ Thẫm 2 - Sát Thương</t>
+          <t>Giai Đoạn Xói Mòn Đỏ Thẫm 2 - Sát Thương</t>
         </is>
       </c>
     </row>
@@ -20789,7 +20789,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>DMG Giai đoạn 1 Sanguine Pulse</t>
+          <t>Sát Thương Giai Đoạn 1 Xung Huyết</t>
         </is>
       </c>
     </row>
@@ -20919,7 +20919,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Tăng Sát Thương Incinerating Will</t>
+          <t>Tăng Sát Thương Ý Chí Thiêu Đốt</t>
         </is>
       </c>
     </row>
@@ -21049,7 +21049,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>DMG Giai đoạn 2 Sanguine Pulse</t>
+          <t>Sát Thương Giai Đoạn 2 Xung Huyết</t>
         </is>
       </c>
     </row>
@@ -21114,7 +21114,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>DMG Giai đoạn 3 Sanguine Pulse</t>
+          <t>Sát Thương Giai Đoạn 3 Xung Huyết</t>
         </is>
       </c>
     </row>
@@ -21179,7 +21179,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Thời Gian Duy Trì Incinerating Will</t>
+          <t>Thời Gian Duy Trì Ý Chí Thiêu Đốt</t>
         </is>
       </c>
     </row>
@@ -21244,7 +21244,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Sát Thương Attack Liên Tiếp</t>
+          <t>Sát Thương Tấn Công Liên Tiếp</t>
         </is>
       </c>
     </row>
@@ -21309,7 +21309,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>DMG Scarlet Burst</t>
+          <t>Sát Thương Bùng Nổ Đỏ Thẫm</t>
         </is>
       </c>
     </row>
@@ -21374,7 +21374,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Resonance Cost</t>
+          <t>Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -21634,7 +21634,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>DMG Chaoscleave</t>
+          <t>Sát Thương Bản Giao Hưởng Hỗn Độn</t>
         </is>
       </c>
     </row>
@@ -21699,7 +21699,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>DMG Scatterbloom</t>
+          <t>Sát Thương Hoa Phân Tán</t>
         </is>
       </c>
     </row>
@@ -21764,7 +21764,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>DMG Chaoscleave khi đầy Energy</t>
+          <t>Sát Thương Chaoscleave Đầy Năng Lượng</t>
         </is>
       </c>
     </row>
@@ -21829,7 +21829,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>DMG Scatterbloom khi đầy Energy</t>
+          <t>Sát Thương Hoa Tán Nở Đầy Năng Lượng</t>
         </is>
       </c>
     </row>
@@ -21959,7 +21959,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Healing Bản Giao Hưởng Hỗn Độn</t>
+          <t>Hồi Phục Bản Giao Hưởng Hỗn Độn</t>
         </is>
       </c>
     </row>
@@ -22024,7 +22024,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Stage 1 DMG</t>
+          <t>Sát Thương Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -22089,7 +22089,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Stage 2 DMG</t>
+          <t>Sát Thương Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Stage 3 DMG</t>
+          <t>Sát Thương Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -22219,7 +22219,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Stage 4 DMG</t>
+          <t>Sát Thương Giai Đoạn 4</t>
         </is>
       </c>
     </row>
@@ -22284,7 +22284,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Chi phí Thể lực cho Heavy Attack</t>
+          <t>Chi phí STA cho Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -22349,7 +22349,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Giảm Sát Thương Heavy Attack</t>
+          <t>Giảm Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack</t>
+          <t>Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -22479,7 +22479,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>DMG Strategic Parry</t>
+          <t>Sát Thương Né Tránh Chiến Thuật</t>
         </is>
       </c>
     </row>
@@ -22544,7 +22544,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>tăng {0} DEF</t>
+          <t>Phòng Ngự</t>
         </is>
       </c>
     </row>
@@ -22609,7 +22609,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>DMG Giai đoạn 1 Timed Counters</t>
+          <t>Sát Thương Giai Đoạn 1 Phản Đòn Định Thời</t>
         </is>
       </c>
     </row>
@@ -22674,7 +22674,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Tăng {0} DEF</t>
+          <t>Phòng Ngự</t>
         </is>
       </c>
     </row>
@@ -22739,7 +22739,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>DMG Giai đoạn 2 Timed Counters</t>
+          <t>Sát Thương Giai Đoạn 2 Phản Đòn Định Thời</t>
         </is>
       </c>
     </row>
@@ -22804,7 +22804,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>{0} DEF</t>
+          <t>Phòng Ngự</t>
         </is>
       </c>
     </row>
@@ -22869,7 +22869,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>DMG Giai đoạn 3 Timed Counters</t>
+          <t>Sát Thương Giai Đoạn 3 Phản Đòn Định Thời</t>
         </is>
       </c>
     </row>
@@ -22934,7 +22934,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Tăng {0} DEF</t>
+          <t>Phòng Ngự</t>
         </is>
       </c>
     </row>
@@ -23129,7 +23129,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -23194,7 +23194,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -23259,7 +23259,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -23389,7 +23389,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Giảm Sát Thương Rocksteady Shield</t>
+          <t>Giảm Sát Thương Khiên Vững Chãi</t>
         </is>
       </c>
     </row>
@@ -23519,7 +23519,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Tăng {0} DEF</t>
+          <t>Phòng Ngự</t>
         </is>
       </c>
     </row>
@@ -23584,7 +23584,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Resonance Cost</t>
+          <t>Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -23649,7 +23649,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -23779,7 +23779,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Đang kích hoạt Khả Năng Healing</t>
+          <t>Đang kích hoạt Khả Năng Hồi Phục</t>
         </is>
       </c>
     </row>
@@ -23844,7 +23844,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -23909,7 +23909,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Tăng {0} DEF</t>
+          <t>Phòng Ngự</t>
         </is>
       </c>
     </row>
@@ -24039,7 +24039,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Lá Chắn Value Cố Định Stage 1 Phản Đòn Định Thời</t>
+          <t>Lá Chắn Giá Trị Cố Định Giai Đoạn 1 Phản Đòn Định Thời</t>
         </is>
       </c>
     </row>
@@ -24104,7 +24104,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Lá Chắn Value Cố Định Stage 2 Phản Đòn Định Thời</t>
+          <t>Lá Chắn Giá Trị Cố Định Giai Đoạn 2 Phản Đòn Định Thời</t>
         </is>
       </c>
     </row>
@@ -24169,7 +24169,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Stage 1 DMG</t>
+          <t>Sát Thương Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Stage 2 DMG</t>
+          <t>Sát Thương Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -24299,7 +24299,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Stage 3 DMG</t>
+          <t>Sát Thương Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -24364,7 +24364,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Stage 4 DMG</t>
+          <t>Sát Thương Giai Đoạn 4</t>
         </is>
       </c>
     </row>
@@ -24429,7 +24429,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>DMG Giai đoạn 5</t>
+          <t>Sát Thương Giai Đoạn 5</t>
         </is>
       </c>
     </row>
@@ -24624,7 +24624,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>DMG của Aimed Shot</t>
+          <t>Sát Thương Bắn Tỉa</t>
         </is>
       </c>
     </row>
@@ -24689,7 +24689,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>DMG của Aimed Shot Nạp Đầy</t>
+          <t>Sát Thương Bắn Chính Xác Đã Nạp Đầy</t>
         </is>
       </c>
     </row>
@@ -24754,7 +24754,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -24819,7 +24819,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Sát thương Đạn Mist</t>
+          <t>Sát thương Đạn Sương mù</t>
         </is>
       </c>
     </row>
@@ -24884,7 +24884,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>{0} per Missile</t>
+          <t>Tăng {0} mỗi tên lửa</t>
         </is>
       </c>
     </row>
@@ -25014,7 +25014,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -25079,7 +25079,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>HP Hóa thân Mist</t>
+          <t>HP Hóa thân Sương mù</t>
         </is>
       </c>
     </row>
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Thời gian Hóa thân Mist</t>
+          <t>Thời gian Hóa thân Sương mù</t>
         </is>
       </c>
     </row>
@@ -25209,7 +25209,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Increase Tấn Công Cổng Băn Khoăn</t>
+          <t>Tăng ATK Cổng Băn Khoăn</t>
         </is>
       </c>
     </row>
@@ -25274,7 +25274,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Resonance Cost</t>
+          <t>Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -25339,7 +25339,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -25404,7 +25404,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -25469,7 +25469,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Increase Movement Speed</t>
+          <t>Tăng Tốc Độ Di Chuyển</t>
         </is>
       </c>
     </row>
@@ -25534,7 +25534,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Sát thương Đạn Mist</t>
+          <t>DMG Đạn Sương mù</t>
         </is>
       </c>
     </row>
@@ -25599,7 +25599,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Stage 1 DMG</t>
+          <t>Sát Thương Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -25664,7 +25664,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Stage 2 DMG</t>
+          <t>Sát Thương Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -25729,7 +25729,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Stage 3 DMG</t>
+          <t>Sát Thương Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Stage 4 DMG</t>
+          <t>Sát Thương Giai Đoạn 4</t>
         </is>
       </c>
     </row>
@@ -25859,7 +25859,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Stage 1 DMG Mid-air Attack</t>
+          <t>Sát Thương Giai Đoạn 1 Mid-air Attack</t>
         </is>
       </c>
     </row>
@@ -25924,7 +25924,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Stage 2 DMG Mid-air Attack</t>
+          <t>Sát Thương Giai Đoạn 2 Mid-air Attack</t>
         </is>
       </c>
     </row>
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>DMG của Aimed Shot</t>
+          <t>Sát Thương Bắn Tỉa</t>
         </is>
       </c>
     </row>
@@ -26119,7 +26119,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>DMG của Aimed Shot Nạp Đầy</t>
+          <t>Sát Thương Bắn Chính Xác Đã Nạp Đầy</t>
         </is>
       </c>
     </row>
@@ -26184,7 +26184,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -26249,7 +26249,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -26314,7 +26314,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -26444,7 +26444,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>DMG Violent Finale</t>
+          <t>Sát Thương Kết Cục Đẫm Máu</t>
         </is>
       </c>
     </row>
@@ -26509,7 +26509,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>DMG Marcato</t>
+          <t>Sát Thương Marcato</t>
         </is>
       </c>
     </row>
@@ -26574,7 +26574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Thời gian</t>
+          <t>Thời lượng</t>
         </is>
       </c>
     </row>
@@ -26704,7 +26704,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -26834,7 +26834,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Resonance Cost</t>
+          <t>Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -26899,7 +26899,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>DMG Fury Fugue</t>
+          <t>Sát Thương Khúc Phẫn Nộ</t>
         </is>
       </c>
     </row>
@@ -27224,7 +27224,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Giai đoạn 4 Basic Attack: Annoyance</t>
+          <t>Cú Đòn Cơ Bản Hạng 4: Phiền Toái</t>
         </is>
       </c>
     </row>
@@ -27289,7 +27289,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Heavy Attack: Phiền Toái</t>
+          <t>Đòn Heavy Attack: Phiền Toái</t>
         </is>
       </c>
     </row>
@@ -27354,7 +27354,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Heavy Attack Nảy Mũi: Phiền Phức</t>
+          <t>Đòn Heavy Attack Nảy Mũi: Phiền Phức</t>
         </is>
       </c>
     </row>
@@ -27484,7 +27484,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Dissonance: Annoyance</t>
+          <t>Bất Hòa: Phiền Não</t>
         </is>
       </c>
     </row>
@@ -27549,7 +27549,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Dodge Counter: Annoyance</t>
+          <t>Dodge Counter: Phiền Toái</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Passionate Variation: Annoyance</t>
+          <t>Biến Thể Nhiệt Huyết: Phiền Muộn</t>
         </is>
       </c>
     </row>
@@ -27679,7 +27679,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Stage 1 DMG</t>
+          <t>Sát Thương Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -27744,7 +27744,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Stage 2 DMG</t>
+          <t>Sát Thương Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -27809,7 +27809,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Stage 3 DMG</t>
+          <t>Sát Thương Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Stage 4 DMG</t>
+          <t>Sát Thương Giai Đoạn 4</t>
         </is>
       </c>
     </row>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack</t>
+          <t>Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -28004,7 +28004,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack Full Năng Lượng</t>
+          <t>Sát Thương Đòn Heavy Attack Đầy Năng Lượng</t>
         </is>
       </c>
     </row>
@@ -28199,7 +28199,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -28264,7 +28264,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -28394,7 +28394,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Nhận Thermobaric Bullets</t>
+          <t>Nhận Đạn Nhiệt Áp</t>
         </is>
       </c>
     </row>
@@ -28524,7 +28524,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -28589,7 +28589,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Nhận Thermobaric Bullets</t>
+          <t>Nhận Đạn Nhiệt Áp</t>
         </is>
       </c>
     </row>
@@ -28654,7 +28654,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Resonance Cost</t>
+          <t>Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -28914,7 +28914,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Sát Thương Thermobaric Bullets</t>
+          <t>Sát Thương Đạn Nhiệt Áp</t>
         </is>
       </c>
     </row>
@@ -28979,7 +28979,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>DMG Boom Boom</t>
+          <t>Sát Thương Bùm Bùm</t>
         </is>
       </c>
     </row>
@@ -29044,7 +29044,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Hồi Concerto Energy từ Thermobaric Bullet</t>
+          <t>Khúc Tái Sinh Đạn Nhiệt Áp</t>
         </is>
       </c>
     </row>
@@ -29109,7 +29109,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Hồi Concerto Energy từ DAKA DAKA!</t>
+          <t>DAKA DAKA! Concerto Regen</t>
         </is>
       </c>
     </row>
@@ -29174,7 +29174,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -29239,7 +29239,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Nhận Thermobaric Bullets</t>
+          <t>Nhận Đạn Nhiệt Áp</t>
         </is>
       </c>
     </row>
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Resonance Cost</t>
+          <t>Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -29824,7 +29824,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -29954,7 +29954,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>DMG Blazing Waltz</t>
+          <t>Sát Thương Vũ Điệu Rực Lửa</t>
         </is>
       </c>
     </row>
@@ -30019,7 +30019,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Tiêu hao STA Vining Waltz 1</t>
+          <t>Chi phí STA Vining Waltz 1</t>
         </is>
       </c>
     </row>
@@ -30084,7 +30084,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Tiêu hao STA Vining Waltz 2</t>
+          <t>Chi phí STA Vining Waltz 2</t>
         </is>
       </c>
     </row>
@@ -30149,7 +30149,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Tiêu hao STA Vining Waltz 3</t>
+          <t>Chi phí STA Vining Waltz 3</t>
         </is>
       </c>
     </row>
@@ -30214,7 +30214,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Tiêu hao STA Vining Waltz 4</t>
+          <t>Chi phí STA Vining Waltz 4</t>
         </is>
       </c>
     </row>
@@ -30279,7 +30279,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Tiêu hao STA Blazing Waltz</t>
+          <t>Tiêu Hao STA Vũ Điệu Rực Lửa</t>
         </is>
       </c>
     </row>
@@ -30344,7 +30344,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Tiêu hao STA Vining Ronde</t>
+          <t>Tiêu Hao STA Vòng Dây Leo</t>
         </is>
       </c>
     </row>
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Bói Kiếm Quyển: Dùng {1}. Gây sát thương và phục hồi HP. Tạo ngẫu nhiên một món Đồ Cổ.</t>
+          <t>Bói Kiếm Quyển: Dùng {1}. Gây DMG và phục hồi HP. Tạo ngẫu nhiên một món Đồ Cổ.</t>
         </is>
       </c>
     </row>
@@ -30669,7 +30669,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Art of Violence: {Cus:Ipt,Touch=Touch PC=press Gamepad=press} {0} để tấn công và khống chế mục tiêu, hồi phục Tinh Thể Linh Hoạt. {Cus:Ipt,Touch=Touch PC=press Gamepad=press} {0} lần nữa trong thời gian giới hạn để tiêu thụ toàn bộ Tinh Thể Linh Hoạt và tấn công mục tiêu. Khôi phục Thanh Forte dựa trên số lượng Tinh Thể Linh Hoạt đã tiêu thụ.</t>
+          <t>Nghệ Thuật Bạo Lực: {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} {0} để tấn công và khống chế mục tiêu, hồi phục Tinh Thể Linh Hoạt. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} {0} lần nữa trong thời gian giới hạn để tiêu thụ toàn bộ Tinh Thể Linh Hoạt và tấn công mục tiêu. Khôi phục Thanh Forte dựa trên số lượng Tinh Thể Linh Hoạt đã tiêu thụ.</t>
         </is>
       </c>
     </row>
@@ -30734,7 +30734,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Heavy Attack - Hư Vô Sắp Tới: Khi Tinh Thể Nhuộm không trong Cooldown chiêu và Thanh Forte đầy, giữ {0} để tấn công mục tiêu, giảm Cooldown chiêu Resonance Skill.</t>
+          <t>Tấn Công Mạnh - Hư Vô Sắp Tới: Khi Tinh Thể Nhuộm không trong thời gian hồi chiêu và Thanh Forte đầy, giữ {0} để tấn công mục tiêu, giảm thời gian hồi chiêu Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -30799,7 +30799,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Kỷ Nguyên Sóng New: {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} để tấn công mục tiêu và bước vào trạng thái đặc biệt. Trong trạng thái này, hãy liên tiếp tung ra tối đa 4 đòn đánh bằng cách {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} hoặc {1} liên tục trong thời gian giới hạn. Sau đó, kết thúc bằng một đòn kết liễu mạnh mẽ bằng cách {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} hoặc {1}.</t>
+          <t>Kỷ Nguyên Sóng Mới: {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} {0} để tấn công mục tiêu và bước vào trạng thái đặc biệt. Trong trạng thái này, hãy liên tiếp tung ra tối đa 4 đòn đánh bằng cách {Cus:Ipt,Touch=tapping PC=pressing Gamepad=pressing} {0} hoặc {1} liên tục trong thời gian giới hạn. Sau đó, kết thúc bằng một đòn kết liễu mạnh mẽ bằng cách {Cus:Ipt,Touch=tapping PC=pressing Gamepad=pressing} {0} hoặc {1}.</t>
         </is>
       </c>
     </row>
@@ -30864,7 +30864,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Heavy Attack - Hy Sinh Lửa: Giữ {0} khi đứng trên mặt đất và Thanh Forte đạt 4 tầng.</t>
+          <t>Tấn Công Mạnh - Hy Sinh Lửa: Giữ {0} khi đứng trên mặt đất và Thanh Forte đạt 4 tầng.</t>
         </is>
       </c>
     </row>
@@ -30929,7 +30929,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Kỹ Năng Basic: Chân Tướng - Chinh Phục: Khi ở trạng thái Chân Tướng, sử dụng {0} khi đang trên mặt đất.</t>
+          <t>Kỹ Năng Cơ Bản: Chân Tướng - Chinh Phục: Khi ở trạng thái Chân Tướng, sử dụng {0} khi đang trên mặt đất.</t>
         </is>
       </c>
     </row>
@@ -31059,7 +31059,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Heavy Attack - Khúc Rhapsody: Giữ {0} sau Basic Attack Stage 2 hoặc 4, hoặc {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} khi tiếp đất sau Mid-air Attack Stage 4 để thi triển.</t>
+          <t>Heavy Attack - Khúc Rhapsody: Giữ {0} sau Basic Attack Giai Đoạn 2 hoặc 4, hoặc {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} khi tiếp đất sau Tấn Công Giữa Không Giai Đoạn 4 để thi triển.</t>
         </is>
       </c>
     </row>
@@ -31124,7 +31124,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Heavy Attack - Gặm Nhấm Của Sói: Khi có ít nhất 50 điểm Ngọn Lửa Sói, giữ {0}.</t>
+          <t>Đòn Heavy Attack - Gặm Nhấm Của Sói: Khi có ít nhất 50 điểm Ngọn Lửa Sói, giữ {0}.</t>
         </is>
       </c>
     </row>
@@ -31189,7 +31189,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Heavy Attack - Vuốt Sói: Khi có ít nhất 50 điểm Ngọn Lửa Sói và 1 điểm Đức Tin Sói, giữ {0}.</t>
+          <t>Đòn Heavy Attack - Vuốt Sói: Khi có ít nhất 50 điểm Ngọn Lửa Sói và 1 điểm Đức Tin Sói, giữ {0}.</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Basic Attack - Sao Băng Rơi: Giữ {0} khi đang ở trên không, rồi {Cus:Ipt,Touch=bấm PC=press Gamepad=press} {0} khi tiếp đất.</t>
+          <t>Basic Attack - Sao Băng Rơi: Giữ {0} khi đang ở trên không, rồi {Cus:Ipt,Touch=tap PC=click Gamepad=press} {0} khi tiếp đất.</t>
         </is>
       </c>
     </row>
@@ -31319,7 +31319,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Pack Hunt: Resonance Liberation của Lupa sẽ kích hoạt Pack Hunt cho Resonators khác trong đội, gia tăng thêm Tấn Công Bổ Sung. Intro Skill của tất cả Resonators trong đội sẽ tăng cường hiệu ứng của Pack Hunt.</t>
+          <t>Săn Đoàn: Resonance Liberation của Lupa sẽ kích hoạt Săn Đoàn cho các Resonator khác trong đội, gia tăng thêm Tấn Công Bổ Sung. Kỹ Năng Khởi Động của tất cả Resonator trong đội sẽ tăng cường hiệu ứng của Săn Đoàn.</t>
         </is>
       </c>
     </row>
@@ -31384,7 +31384,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Intro Skill - Không Nơi Trốn Chạy!: Có thể sử dụng khi Pack Hunt được nâng cấp toàn diện.</t>
+          <t>Kỹ Năng Khởi Động - Không Nơi Trốn Chạy!: Có thể sử dụng khi Pack Hunt được nâng cấp toàn diện.</t>
         </is>
       </c>
     </row>
@@ -31449,7 +31449,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Basic Attack trúng mục tiêu sẽ hồi phục &lt;color=Highlight&gt;Relative Momentum&lt;/color&gt;.</t>
+          <t>Basic Attack trúng mục tiêu sẽ hồi phục &lt;color=Highlight&gt;Động Lượng Tương Đối&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Khi ở &lt;color=Highlight&gt;Wide Field Observation Mode&lt;/color&gt;, Basic Attack và Resonance Skill hồi phục &lt;color=Highlight&gt;Relative Momentum&lt;/color&gt; khi trúng mục tiêu.</t>
+          <t>Khi ở &lt;color=Highlight&gt;Chế Độ Quan Sát Trường Rộng&lt;/color&gt;, Đòn Basic Attack và Resonance Skill hồi phục &lt;color=Highlight&gt;Động Lượng Tương Đối&lt;/color&gt; khi trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -31579,7 +31579,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Khải Tường: Dùng {0} trong vòng 5 giây sau khi thi triển Stage 4 của Incarnation - Basic Attack.</t>
+          <t>Khải Tường: Dùng {0} trong vòng 5 giây sau khi thi triển Giai Đoạn 4 của Hóa Thân - Đòn Cơ Bản.</t>
         </is>
       </c>
     </row>
@@ -31644,7 +31644,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Incarnation: Sau khi tung Basic Attack 4 hoặc Intro Skill, sử dụng {0} trong vòng 5 giây khi Resonance Skill chưa Cooldown.</t>
+          <t>Hóa Thân: Sau khi tung Basic Attack 4 hoặc Kỹ Năng Khởi Động, sử dụng {0} trong vòng 5 giây khi Resonance Skill chưa Thời gian hồi.</t>
         </is>
       </c>
     </row>
@@ -31709,7 +31709,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Sát thương Attack 1 Basic 1</t>
+          <t>DMG Basic Attack 1</t>
         </is>
       </c>
     </row>
@@ -31774,7 +31774,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Sát thương Basic Attack 2</t>
+          <t>DMG Basic Attack 2</t>
         </is>
       </c>
     </row>
@@ -31839,7 +31839,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Sát thương Basic Attack 3</t>
+          <t>DMG Basic Attack 3</t>
         </is>
       </c>
     </row>
@@ -31904,7 +31904,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Sát thương Basic Attack 4</t>
+          <t>DMG Basic Attack 4</t>
         </is>
       </c>
     </row>
@@ -31969,7 +31969,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Sát thương Basic Attack 5</t>
+          <t>DMG Basic Attack 5</t>
         </is>
       </c>
     </row>
@@ -32034,7 +32034,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack</t>
+          <t>Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -32164,7 +32164,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -32229,7 +32229,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Chi phí Thể lực cho Heavy Attack</t>
+          <t>Chi phí STA cho Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -32359,7 +32359,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>DMG Crimson Blossom</t>
+          <t>Sát Thương Hoa Đỏ Thẫm</t>
         </is>
       </c>
     </row>
@@ -32684,7 +32684,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>DMG Floral Ravage</t>
+          <t>Sát Thương Bản Giao Hưởng Flora Tàn Phá</t>
         </is>
       </c>
     </row>
@@ -32749,7 +32749,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>DMG Vining Ronde</t>
+          <t>Sát Thương Vòng Dây Leo</t>
         </is>
       </c>
     </row>
@@ -32814,7 +32814,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>DMG Atonement</t>
+          <t>Sát Thương Chuộc Tội</t>
         </is>
       </c>
     </row>
@@ -32944,7 +32944,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -33009,7 +33009,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Hồi Concerto Energy từ Crimson Blossom</t>
+          <t>Khúc Hợp Tấu Hoa Đỏ Thẫm - Hồi Phục</t>
         </is>
       </c>
     </row>
